--- a/2026_S1_PHYS1120_SEC_51_grading/data/2026_S1_PHYS1120_attendance.xlsx
+++ b/2026_S1_PHYS1120_SEC_51_grading/data/2026_S1_PHYS1120_attendance.xlsx
@@ -631,51 +631,21 @@
           <t>นางสาวธัญวรัตม์  ชัยทะนัน</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
       <c r="R2" s="3">
         <f>COUNTIF(C2:Q2, "P") + COUNTIF(C2:Q2, "L")*0.8 + COUNTIF(C2:Q2, "EA")</f>
         <v/>
@@ -692,51 +662,21 @@
           <t>นางสาวสุปวีร์  ปันทิ</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
       <c r="R3" s="3">
         <f>COUNTIF(C3:Q3, "P") + COUNTIF(C3:Q3, "L")*0.8 + COUNTIF(C3:Q3, "EA")</f>
         <v/>
@@ -753,51 +693,21 @@
           <t>นายฐิตากร  สุนะคำ</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
       <c r="R4" s="3">
         <f>COUNTIF(C4:Q4, "P") + COUNTIF(C4:Q4, "L")*0.8 + COUNTIF(C4:Q4, "EA")</f>
         <v/>
@@ -814,51 +724,21 @@
           <t>นายณัฐวัศ  ก๋ายศ</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
       <c r="R5" s="3">
         <f>COUNTIF(C5:Q5, "P") + COUNTIF(C5:Q5, "L")*0.8 + COUNTIF(C5:Q5, "EA")</f>
         <v/>
@@ -875,51 +755,21 @@
           <t>นายธนากานต์  ไขปัญญา</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
       <c r="R6" s="3">
         <f>COUNTIF(C6:Q6, "P") + COUNTIF(C6:Q6, "L")*0.8 + COUNTIF(C6:Q6, "EA")</f>
         <v/>
@@ -936,51 +786,21 @@
           <t>นายบุรชัย  นงรัตน์</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
       <c r="R7" s="3">
         <f>COUNTIF(C7:Q7, "P") + COUNTIF(C7:Q7, "L")*0.8 + COUNTIF(C7:Q7, "EA")</f>
         <v/>
@@ -997,51 +817,21 @@
           <t>นายพัชรพล  คุมา</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
       <c r="R8" s="3">
         <f>COUNTIF(C8:Q8, "P") + COUNTIF(C8:Q8, "L")*0.8 + COUNTIF(C8:Q8, "EA")</f>
         <v/>
@@ -1058,51 +848,21 @@
           <t>นายรัฐธรรมนูญ  เตมีศักดิ์</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
       <c r="R9" s="3">
         <f>COUNTIF(C9:Q9, "P") + COUNTIF(C9:Q9, "L")*0.8 + COUNTIF(C9:Q9, "EA")</f>
         <v/>
@@ -1119,51 +879,21 @@
           <t>นายวรากรณ์  คิดชัย</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
       <c r="R10" s="3">
         <f>COUNTIF(C10:Q10, "P") + COUNTIF(C10:Q10, "L")*0.8 + COUNTIF(C10:Q10, "EA")</f>
         <v/>
@@ -1180,51 +910,21 @@
           <t>นายเสฏฐวุฒิ  มณีเพชรมงคล</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
       <c r="R11" s="3">
         <f>COUNTIF(C11:Q11, "P") + COUNTIF(C11:Q11, "L")*0.8 + COUNTIF(C11:Q11, "EA")</f>
         <v/>
@@ -1241,51 +941,21 @@
           <t>นางสาวชณัญธิดา  ดำแดงดี</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
       <c r="R12" s="3">
         <f>COUNTIF(C12:Q12, "P") + COUNTIF(C12:Q12, "L")*0.8 + COUNTIF(C12:Q12, "EA")</f>
         <v/>
@@ -1302,51 +972,21 @@
           <t>นายกิตติชัย  แซ่ย้า</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
       <c r="R13" s="3">
         <f>COUNTIF(C13:Q13, "P") + COUNTIF(C13:Q13, "L")*0.8 + COUNTIF(C13:Q13, "EA")</f>
         <v/>
@@ -1363,51 +1003,21 @@
           <t>นายเกียรติศักดิ์  คำมินทร์</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
       <c r="R14" s="3">
         <f>COUNTIF(C14:Q14, "P") + COUNTIF(C14:Q14, "L")*0.8 + COUNTIF(C14:Q14, "EA")</f>
         <v/>
@@ -1424,51 +1034,21 @@
           <t>นายณัฐชนน  สุคะโต</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
       <c r="R15" s="3">
         <f>COUNTIF(C15:Q15, "P") + COUNTIF(C15:Q15, "L")*0.8 + COUNTIF(C15:Q15, "EA")</f>
         <v/>
@@ -1485,51 +1065,21 @@
           <t>นางสาวกรรณิการ์  สุยะหมี</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
       <c r="R16" s="3">
         <f>COUNTIF(C16:Q16, "P") + COUNTIF(C16:Q16, "L")*0.8 + COUNTIF(C16:Q16, "EA")</f>
         <v/>
@@ -1546,51 +1096,21 @@
           <t>นายคณานนท์  โพธินาม</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
       <c r="R17" s="3">
         <f>COUNTIF(C17:Q17, "P") + COUNTIF(C17:Q17, "L")*0.8 + COUNTIF(C17:Q17, "EA")</f>
         <v/>
@@ -1607,51 +1127,21 @@
           <t>นายวรเมธ  ศศิสุวรรณ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
       <c r="R18" s="3">
         <f>COUNTIF(C18:Q18, "P") + COUNTIF(C18:Q18, "L")*0.8 + COUNTIF(C18:Q18, "EA")</f>
         <v/>
@@ -1668,51 +1158,21 @@
           <t>นายวัสณานฤวาส  สีอึ่ง</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
       <c r="R19" s="3">
         <f>COUNTIF(C19:Q19, "P") + COUNTIF(C19:Q19, "L")*0.8 + COUNTIF(C19:Q19, "EA")</f>
         <v/>
@@ -1729,51 +1189,21 @@
           <t>นางสาวอัญติญา  ชื่นบาล</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
       <c r="R20" s="3">
         <f>COUNTIF(C20:Q20, "P") + COUNTIF(C20:Q20, "L")*0.8 + COUNTIF(C20:Q20, "EA")</f>
         <v/>
